--- a/randoms_ER/randoms_ER_annotations_scores_wo_lgl.xlsx
+++ b/randoms_ER/randoms_ER_annotations_scores_wo_lgl.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ku51015\CHMURA\mystuff\Graph-Vizualisation-Rating-Metric-randoms\randoms_ER\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB274FB-23BA-41E2-8707-B3F16F0ACE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4507"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="2652" yWindow="2652" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2655" yWindow="2655" windowWidth="17280" windowHeight="8880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>graph_id</t>
   </si>
@@ -47,15 +41,12 @@
   <si>
     <t>kamada_kawai</t>
   </si>
-  <si>
-    <t>lgl</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,7 +79,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -146,7 +137,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -198,7 +189,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -392,24 +383,24 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.77734375" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -431,11 +422,8 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -458,7 +446,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -481,7 +469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>2</v>
       </c>
@@ -504,7 +492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
@@ -527,7 +515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
@@ -550,7 +538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
@@ -573,7 +561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
@@ -596,7 +584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
@@ -619,7 +607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -642,7 +630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
@@ -662,6 +650,259 @@
         <v>1</v>
       </c>
       <c r="G11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+      <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
         <v>3</v>
       </c>
     </row>
